--- a/output/第10期計画_サービス見込量算定_統合報告書.xlsx
+++ b/output/第10期計画_サービス見込量算定_統合報告書.xlsx
@@ -24878,7 +24878,7 @@
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>内部保管16件</t>
+          <t>内部保管22件</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">

--- a/output/第10期計画_サービス見込量算定_統合報告書.xlsx
+++ b/output/第10期計画_サービス見込量算定_統合報告書.xlsx
@@ -9736,7 +9736,7 @@
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>20.4％（98票中20票）</t>
+          <t>20.2％（99票中20票）</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -9746,7 +9746,7 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>目標が未確定。分母が98票と小さい</t>
+          <t>目標が未確定。分母が99票と小さい</t>
         </is>
       </c>
     </row>
@@ -24878,7 +24878,7 @@
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>内部保管22件</t>
+          <t>内部保管23件</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">

--- a/output/第10期計画_サービス見込量算定_統合報告書.xlsx
+++ b/output/第10期計画_サービス見込量算定_統合報告書.xlsx
@@ -1912,7 +1912,7 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>約4.3か月分</t>
+          <t>約4.1か月分</t>
         </is>
       </c>
       <c r="E8" s="14" t="inlineStr">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>約4.3か月分だが値は使える</t>
+          <t>約4.1か月分だが値は使える</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
@@ -1976,7 +1976,7 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>約4.3か月分だが値は使える</t>
+          <t>約4.1か月分だが値は使える</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
@@ -2025,8 +2025,8 @@
     <row r="12" ht="48" customHeight="1">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>注1）令和8年度の給付費は令和7年度の36.0％であり、月数に換算するとおおむね4.3か月分に当たります。月数そのものは公表されていないため［要確認］です。
-注2）令和6年度と令和8年度は3町合計と広域連合単位が完全に一致し、令和7年度のみ4.0％の差があります（確認事項No.87）。</t>
+          <t>注1）令和8年度の給付費は令和7年度の34.5％であり、月数に換算するとおおむね4.1か月分に当たります。月数そのものは公表されていないため［要確認］です。
+注2）3町のファイルの合計と広域連合単位のファイルは、令和6年度から令和8年度まで円単位で一致します。令和7年度にあった129,580,267円の差は、令和8年9月25日に再提供を受けたファイルにより解消しました（確認事項No.87）。</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3469,7 @@
     <row r="41" ht="32" customHeight="1">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>計画作成支援ツールの給付費（広域連合の行）</t>
+          <t>給付費データ集計（広域連合単位のファイル）</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>3,083,474,291</t>
+          <t>3,213,054,558</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
@@ -3491,14 +3491,14 @@
       <c r="F41" s="5" t="n"/>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>令和6年度は決算の保険給付費＋介護予防・生活支援サービス事業費とおおむね一致する。年報の給付費とは範囲が異なる</t>
+          <t>「給付費総額」（保険請求額＋保険利用者負担額）の合計であり費用額に当たる。年報の給付費とは範囲が異なる</t>
         </is>
       </c>
     </row>
     <row r="42" ht="32" customHeight="1">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>計画作成支援ツールの給付費（3町の行の合計）</t>
+          <t>給付費データ集計（3町のファイルの合計）</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
@@ -3520,7 +3520,7 @@
       <c r="F42" s="5" t="n"/>
       <c r="G42" s="5" t="inlineStr">
         <is>
-          <t>令和6年度・令和8年度は広域連合の行と完全に一致し、令和7年度のみ129,580,267円（4.2％）上回る（確認事項No.87）</t>
+          <t>令和6年度から令和8年度まで広域連合単位のファイルと完全に一致する。令和7年度にあった129,580,267円の差は、令和8年9月25日に再提供を受けたファイルにより解消した（確認事項No.87）</t>
         </is>
       </c>
     </row>
@@ -3578,14 +3578,14 @@
       <c r="F44" s="5" t="n"/>
       <c r="G44" s="5" t="inlineStr">
         <is>
-          <t>計画作成支援ツールの給付費合計との差は-5,775円</t>
+          <t>給付費データ集計の合計との差は-5,775円</t>
         </is>
       </c>
     </row>
     <row r="45" ht="34" customHeight="1">
       <c r="A45" s="9" t="inlineStr">
         <is>
-          <t>注）計画作成支援ツールの給付費合計は、令和6年度において決算の保険給付費（款2）に介護予防・生活支援サービス事業費を加えた額と5,775円の差で一致します。ツールの給付費は総合事業費を含む範囲であるとみられます。［要確認］</t>
+          <t>注）給付費データ集計の給付費（給付費総額）の合計は、令和6年度において決算の保険給付費（款2）に介護予防・生活支援サービス事業費を加えた額と5,775円の差で一致します。給付費データの給付費総額は総合事業費を含む範囲であるとみられます。［要確認］</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
-          <t>3町合計は町をまたぐ計上の重複を含み、令和7年度の給付費で広域連合単位を4.0％上回る（確認事項No.87）。保険料は保険者単位で算定するため、算定の基礎には用いられない。町別の実績を掲げる用途には用いる。</t>
+          <t>3町合計は利用者数において広域連合単位を大きく上回る（区域外の施設を利用する被保険者と区域内の施設を利用する他保険者の被保険者の扱いが違う）。保険料は保険者単位で算定するため、算定の基礎には用いられない。町別の実績を掲げる用途には用いる。</t>
         </is>
       </c>
     </row>
@@ -6344,17 +6344,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>3町合計と広域連合単位の給付費の差が令和7年度のみに生じること</t>
+          <t>3町合計と広域連合単位の給付費がいずれの年度も一致すること</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>R6 0円／R7 129,580,267円／R8 0円</t>
+          <t>R6 0円／R7 0円／R8 0円</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>令和6年度・令和8年度は一致、令和7年度のみ4.2％の差</t>
+          <t>3か年とも円単位で一致（令和7年度の差は再提供により解消した）</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>3町合計と広域連合単位の給付費の差（令和7年度4.0％）</t>
+          <t>給付費データの給付費総額と年報の給付費の範囲の違い</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>確認事項No.87として照会中である。本表では広域連合単位を用いている</t>
+          <t>給付費総額は保険請求額＋保険利用者負担額であり費用額に当たる。本表の算定は年報及び総括表（保険給付費）によっている</t>
         </is>
       </c>
       <c r="D21" s="5" t="n"/>
@@ -6622,7 +6622,7 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>給付費が令和7年度の36.0％であることから、おおむね4.3か月分と見ているが、月数そのものは公表されていない。令和8年度を実績として掲げる場合、月数の明記が要る。</t>
+          <t>給付費が令和7年度の34.5％であることから、おおむね4.1か月分と見ているが、月数そのものは公表されていない。令和8年度を実績として掲げる場合、月数の明記が要る。</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -6828,7 +6828,7 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>令和8年度は令和8年4月から7月までの4か月と確定しました。介護保険事業状況報告の月報（data_nenpo.GEPPO）が4か月分を収録しています。使いづらい主因は季節ではなく単価です。給付費は令和7年度の36.00％で4.320か月相当ですが、数量は月報で+1.99％にとどまり期待は4.079か月相当です。残差は単価であり、分母の採り方で+1.63％から+5.90％の幅があります。</t>
+          <t>令和8年度は令和8年4月から7月までの4か月と確定しました。介護保険事業状況報告の月報（data_nenpo.GEPPO）が4か月分を収録しています。使いづらい主因は季節ではなく単価です。給付費は令和7年度の34.55％で4.146か月相当ですが、数量は月報で+1.99％にとどまり期待は4.079か月相当です。残差は単価であり、分母の採り方で+1.63％から+1.63％の幅があります。</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
@@ -6973,7 +6973,7 @@
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>①令和8年度の月数は月報により4か月と確定しました（当初は給付費の比から約4.3か月と推計していました）。②単価の残差は確認事項No.87の未解決により＋1.63％から＋5.90％の幅があります（当初は＋5.90％と単一の値で示していました）。③居住系の季節性は測定できません（当初は有意としていました）。</t>
+          <t>①令和8年度の月数は月報により4か月と確定しました（当初は給付費の比から約4.3か月と推計していました）。②単価の残差は＋1.63％です（当初は＋5.90％としていました。確認事項No.87の決着により分母が一つに定まりました）。③居住系の季節性は測定できません（当初は有意としていました）。</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>0.3600</t>
+          <t>0.3455</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
@@ -8047,7 +8047,7 @@
       <c r="E8" s="5" t="n"/>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>12を乗じると4.320か月相当。月数4か月と一致しない</t>
+          <t>12を乗じると4.146か月相当。月数4か月と一致しない</t>
         </is>
       </c>
     </row>
@@ -8163,7 +8163,7 @@
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>3　残差＝単価（分母の採り方で変わる）</t>
+          <t>3　残差＝単価</t>
         </is>
       </c>
     </row>
@@ -8202,7 +8202,7 @@
     <row r="18" ht="24" customHeight="1">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>計画作成支援ツール 3町合計単位</t>
+          <t>給付費データ 広域連合単位</t>
         </is>
       </c>
       <c r="B18" s="11" t="n">
@@ -8228,34 +8228,34 @@
     <row r="19" ht="24" customHeight="1">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>計画作成支援ツール 広域連合単位</t>
+          <t>給付費データ 3町のファイルの合計</t>
         </is>
       </c>
       <c r="B19" s="11" t="n">
-        <v>0.36</v>
+        <v>0.3455</v>
       </c>
       <c r="C19" s="11" t="n">
-        <v>4.32</v>
+        <v>4.146</v>
       </c>
       <c r="D19" s="11" t="n">
         <v>4.079</v>
       </c>
       <c r="E19" s="10" t="inlineStr">
         <is>
-          <t>+5.90％</t>
+          <t>+1.63％</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>+358円</t>
+          <t>+99円</t>
         </is>
       </c>
     </row>
     <row r="20" ht="76" customHeight="1">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>注1）令和8年度は3町合計と広域連合単位が完全に一致します（差0円）。令和7年度のみ4.20％の差があります（確認事項No.87）。したがって同じ基準で比べるには令和7年度も3町合計を用いる必要がありますが、保険料の算定は保険者単位で行うため広域連合単位を用います。この二律背反により残差は確定できません。
-注2）残差が単価であることは、1人1月あたり給付費の令和8年度÷令和7年度（給付費で加重）が1.0590であることと符合します。
+          <t>注1）3町のファイルの合計と広域連合単位のファイルは、令和6年度から令和8年度まで円単位で一致します（差0円）。令和7年度にあった129,580,267円の差は、令和8年9月25日に再提供を受けたファイルにより解消しました（確認事項No.87）。分母はどちらに採っても同じであり、残差は+1.63％の一つの値に定まりました。
+注2）残差が単価であることは、1人1月あたり給付費の令和8年度÷令和7年度（給付費で加重）が1.0163であることと符合します。
 注3）月額への効きは、採用パターンP3の給付費9020.2百万円に残差を乗じて算定しました。</t>
         </is>
       </c>
@@ -8354,18 +8354,18 @@
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>+1.63％〜+5.90％</t>
+          <t>+1.63％</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>確定できない</t>
+          <t>測定できる</t>
         </is>
       </c>
       <c r="E26" s="5" t="n"/>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>確認事項No.87の解決を要する</t>
+          <t>確認事項No.87の決着により分母が一つに定まった</t>
         </is>
       </c>
     </row>
@@ -9013,7 +9013,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>季節を無視するため、施設を過小に在宅を過大に認識する。また単価の残差（+1.63％〜+5.90％）を年度の水準として固定してしまう。</t>
+          <t>季節を無視するため、施設を過小に在宅を過大に認識する。また単価の残差（+1.63％〜+1.63％）を年度の水準として固定してしまう。</t>
         </is>
       </c>
     </row>
@@ -11047,7 +11047,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -11144,7 +11144,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>確認事項No.87。町をまたぐ計上の重複を含む</t>
+          <t>利用者数において広域連合単位と大きく異なる。給付費は一致する</t>
         </is>
       </c>
     </row>
@@ -11154,21 +11154,21 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>★単価を令和8年度の水準に置く（分母＝広域連合）</t>
+          <t>★現行の置き方（見える化の自然体推計×案C補正）</t>
         </is>
       </c>
       <c r="C7" s="11" t="n">
-        <v>9552.299999999999</v>
+        <v>9483.5</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>6787</v>
+        <v>6740</v>
       </c>
       <c r="E7" s="18" t="n">
-        <v>358</v>
+        <v>312</v>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>残差+5.90％。確認事項No.87の解決を要する</t>
+          <t>パターンP1</t>
         </is>
       </c>
     </row>
@@ -11178,21 +11178,21 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>★現行の置き方（見える化の自然体推計×案C補正）</t>
+          <t>★第1号被保険者負担割合を24％にする</t>
         </is>
       </c>
       <c r="C8" s="11" t="n">
-        <v>9483.5</v>
+        <v>9020.200000000001</v>
       </c>
       <c r="D8" s="11" t="n">
-        <v>6740</v>
+        <v>6739</v>
       </c>
       <c r="E8" s="18" t="n">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>パターンP1</t>
+          <t>政令による</t>
         </is>
       </c>
     </row>
@@ -11202,21 +11202,21 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>★第1号被保険者負担割合を24％にする</t>
+          <t>★基金を1億円取り崩す</t>
         </is>
       </c>
       <c r="C9" s="11" t="n">
         <v>9020.200000000001</v>
       </c>
       <c r="D9" s="11" t="n">
-        <v>6739</v>
+        <v>6120</v>
       </c>
       <c r="E9" s="18" t="n">
-        <v>311</v>
+        <v>-308</v>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>政令による</t>
+          <t>条例第5条第3項</t>
         </is>
       </c>
     </row>
@@ -11226,21 +11226,21 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>★基金を1億円取り崩す</t>
+          <t>★認定者数シナリオを③令和元年水準へ回帰に変える</t>
         </is>
       </c>
       <c r="C10" s="11" t="n">
-        <v>9020.200000000001</v>
+        <v>9382.4</v>
       </c>
       <c r="D10" s="11" t="n">
-        <v>6120</v>
+        <v>6672</v>
       </c>
       <c r="E10" s="18" t="n">
-        <v>-308</v>
+        <v>244</v>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>条例第5条第3項</t>
+          <t>パターンP5</t>
         </is>
       </c>
     </row>
@@ -11250,21 +11250,21 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>★認定者数シナリオを③令和元年水準へ回帰に変える</t>
+          <t>★基準年度を令和6年度に変える</t>
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>9382.4</v>
+        <v>8716.700000000001</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>6672</v>
+        <v>6224</v>
       </c>
       <c r="E11" s="18" t="n">
-        <v>244</v>
+        <v>-204</v>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>パターンP5</t>
+          <t>パターンP6</t>
         </is>
       </c>
     </row>
@@ -11274,21 +11274,21 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>★基準年度を令和6年度に変える</t>
+          <t>★施策反映で認定者数を2％抑制（H01・H02）</t>
         </is>
       </c>
       <c r="C12" s="11" t="n">
-        <v>8716.700000000001</v>
+        <v>8839.799999999999</v>
       </c>
       <c r="D12" s="11" t="n">
-        <v>6224</v>
+        <v>6307</v>
       </c>
       <c r="E12" s="18" t="n">
-        <v>-204</v>
+        <v>-121</v>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>パターンP6</t>
+          <t>目標の達成を前提とする。歯止めを要する</t>
         </is>
       </c>
     </row>
@@ -11298,21 +11298,21 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>★施策反映で認定者数を2％抑制（H01・H02）</t>
+          <t>・単価を令和8年度の水準に置く</t>
         </is>
       </c>
       <c r="C13" s="11" t="n">
-        <v>8839.799999999999</v>
+        <v>9167.1</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>6307</v>
-      </c>
-      <c r="E13" s="18" t="n">
-        <v>-121</v>
+        <v>6527</v>
+      </c>
+      <c r="E13" s="12" t="n">
+        <v>99</v>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>目標の達成を前提とする。歯止めを要する</t>
+          <t>残差+1.63％</t>
         </is>
       </c>
     </row>
@@ -11322,21 +11322,21 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>・単価を令和8年度の水準に置く（分母＝3町合計）</t>
+          <t>・施策反映で認定者数を1％抑制</t>
         </is>
       </c>
       <c r="C14" s="11" t="n">
-        <v>9167.1</v>
+        <v>8930</v>
       </c>
       <c r="D14" s="11" t="n">
-        <v>6527</v>
+        <v>6368</v>
       </c>
       <c r="E14" s="12" t="n">
-        <v>99</v>
+        <v>-61</v>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>残差+1.63％</t>
+          <t>同上</t>
         </is>
       </c>
     </row>
@@ -11346,21 +11346,21 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>・施策反映で認定者数を1％抑制</t>
+          <t xml:space="preserve">　定期巡回を5.0人／月整備（純増・令和10年度から）</t>
         </is>
       </c>
       <c r="C15" s="11" t="n">
-        <v>8930</v>
+        <v>9052.799999999999</v>
       </c>
       <c r="D15" s="11" t="n">
-        <v>6368</v>
-      </c>
-      <c r="E15" s="12" t="n">
-        <v>-61</v>
+        <v>6450</v>
+      </c>
+      <c r="E15" s="11" t="n">
+        <v>22</v>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>同上</t>
+          <t>04シート3</t>
         </is>
       </c>
     </row>
@@ -11370,21 +11370,21 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">　定期巡回を5.0人／月整備（純増・令和10年度から）</t>
+          <t xml:space="preserve">　季節指数で年度換算（令和8年度を使う場合のみ）</t>
         </is>
       </c>
       <c r="C16" s="11" t="n">
-        <v>9052.799999999999</v>
+        <v>9000.700000000001</v>
       </c>
       <c r="D16" s="11" t="n">
-        <v>6450</v>
+        <v>6415</v>
       </c>
       <c r="E16" s="11" t="n">
-        <v>22</v>
+        <v>-13</v>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>04シート3</t>
+          <t>P3を採る限り生じない</t>
         </is>
       </c>
     </row>
@@ -11394,21 +11394,21 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">　季節指数で年度換算（令和8年度を使う場合のみ）</t>
+          <t xml:space="preserve">　定期巡回を5.0人／月整備（訪問介護から振替）</t>
         </is>
       </c>
       <c r="C17" s="11" t="n">
-        <v>9000.700000000001</v>
+        <v>9036.700000000001</v>
       </c>
       <c r="D17" s="11" t="n">
-        <v>6415</v>
+        <v>6439</v>
       </c>
       <c r="E17" s="11" t="n">
-        <v>-13</v>
+        <v>11</v>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>P3を採る限り生じない</t>
+          <t>04シート3</t>
         </is>
       </c>
     </row>
@@ -11418,62 +11418,38 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">　定期巡回を5.0人／月整備（訪問介護から振替）</t>
+          <t xml:space="preserve">　季節補正（採用パターンP3の場合）</t>
         </is>
       </c>
       <c r="C18" s="11" t="n">
-        <v>9036.700000000001</v>
+        <v>9020.200000000001</v>
       </c>
       <c r="D18" s="11" t="n">
-        <v>6439</v>
+        <v>6428</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>04シート3</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="11" t="n">
-        <v>15</v>
-      </c>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　季節補正（採用パターンP3の場合）</t>
-        </is>
-      </c>
-      <c r="C19" s="11" t="n">
-        <v>9020.200000000001</v>
-      </c>
-      <c r="D19" s="11" t="n">
-        <v>6428</v>
-      </c>
-      <c r="E19" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" s="5" t="inlineStr">
-        <is>
           <t>完結年度は季節指数の和が12となり、換算係数1.0000で恒等的に消える</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="72" customHeight="1">
-      <c r="A21" s="9" t="inlineStr">
-        <is>
-          <t>注1）★は月額100円超（意思決定に効く）で9件、・は50〜100円で2件、無印は50円未満（誤差の範囲）で4件です。
+    <row r="20" ht="72" customHeight="1">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>注1）★は月額100円超（意思決定に効く）で8件、・は50〜100円で2件、無印は50円未満（誤差の範囲）で4件です。
 注2）給付費1％あたりの月額は60.7円です。
 注3）季節補正と施策反映は、いずれも基準年度・出所の選択より小さい位置にあります。ご指示の主訴に対する答えは、「補正を要しない置き方（令和7年度基準）を既に採っている」ことになります。
-注4）単価を令和8年度の水準に置く場合の効きは、分母の採り方により+99円から+358円の幅があります。確認事項No.87の解決が要ります。</t>
+注4）単価を令和8年度の水準に置く場合の効きは+99円です。確認事項No.87の決着により分母が一つに定まりました。</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A20:F20"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A21:F21"/>
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11693,17 +11669,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>令和8年度は3町合計と広域連合単位が一致し、令和7年度のみ差があること</t>
+          <t>3町合計と広域連合単位の給付費がいずれの年度も一致すること</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>R6 0円／R7 129,580,267円／R8 0円</t>
+          <t>R6 0円／R7 0円／R8 0円</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>令和7年度のみ4.20％の差</t>
+          <t>3か年とも円単位で一致（確認事項No.87は解決）</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
@@ -11718,17 +11694,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>単価の残差が分母の採り方で変わること（単一の値で断定していないこと）</t>
+          <t>単価の残差が分母の採り方によらず一つに定まること</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>分母3町合計 +1.63％／分母広域連合 +5.90％</t>
+          <t>分母3町合計 +1.63％／分母広域連合 +1.63％</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>幅は4.27％ポイント</t>
+          <t>差は0.0000％ポイント</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
@@ -11918,12 +11894,12 @@
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>分母の採り方により＋1.63％から＋5.90％の幅がある</t>
+          <t>＋1.63％である</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>令和8年度は3町合計と広域連合単位が一致するが、令和7年度のみ4.20％の差がある（確認事項No.87）</t>
+          <t>令和8年9月25日に再提供を受けた給付費データにより令和7年度の差が解消し、分母が一つに定まった（確認事項No.87）</t>
         </is>
       </c>
       <c r="E22" s="5" t="n"/>
@@ -12090,12 +12066,12 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>確認事項No.87（令和7年度のみ3町合計と広域連合単位が4.20％違うこと）の解決</t>
+          <t>第10期の単価をどの水準に置くか</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>令和8年度の単価の残差が、分母を令和7年度の3町合計に採ると＋1.63％、広域連合単位に採ると＋5.90％となり確定できない。月額に直すと+99円から+358円の幅があり、季節補正（-13円）よりはるかに大きい。第10期の単価をどの水準に置くかの判断に直結する。</t>
+          <t>令和8年度の単価の残差は＋1.63％であり、月額に直すと+99円である（分母は確認事項No.87の決着により一つに定まった）。季節補正（-13円）よりはるかに大きい。第10期の単価をどの水準に置くかの判断に直結する。</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -16134,7 +16110,7 @@
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>No.87</t>
+          <t>No.87（解決）</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
@@ -16144,12 +16120,12 @@
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>±620円</t>
+          <t>―</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>3町合計と広域連合単位で129,580,267円（4.0％）の差がある</t>
+          <t>令和8年9月25日の再提供により3町合計と広域連合単位が要介護度別まで円単位で一致した</t>
         </is>
       </c>
     </row>
@@ -25637,7 +25613,7 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>見える化システムの総括表は保険者（広域連合）単位、計画作成支援ツールは3町合計です。同じ令和7年度の利用者数でも、3町合計が保険者単位を+1.4％から+243％上回ります。給付費でも令和7年度は3町合計が4.0％上回ります（確認事項No.87）。</t>
+          <t>見える化システムの総括表は保険者（広域連合）単位、計画作成支援ツールは3町合計です。同じ令和7年度の利用者数でも、3町合計が保険者単位を+1.4％から+243％上回ります。給付費は令和6年度から令和8年度まで3町のファイルの合計と広域連合単位のファイルが円単位で一致します（確認事項No.87は解決）。</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">

--- a/output/第10期計画_サービス見込量算定_統合報告書.xlsx
+++ b/output/第10期計画_サービス見込量算定_統合報告書.xlsx
@@ -22157,7 +22157,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G50"/>
+  <dimension ref="A1:G51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -22356,95 +22356,97 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>令和9年度</t>
+          <t>令和8年度</t>
         </is>
       </c>
       <c r="C11" s="10" t="inlineStr">
         <is>
-          <t>改定（見込み）</t>
+          <t>改定</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>第10期の初年度</t>
+          <t>第9期の最終年度</t>
         </is>
       </c>
       <c r="E11" s="5" t="n"/>
       <c r="F11" s="5" t="n"/>
       <c r="G11" s="5" t="inlineStr">
         <is>
+          <t>令和9年度改定を待たずに実施。職員の処遇改善、生産性向上・協働化の促進等のため。改定率は未告示［要確認］</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>令和9年度</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>改定（見込み）</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>第10期の初年度</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="5" t="n"/>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
           <t>改定率は未告示［要確認］</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="42" customHeight="1">
-      <c r="A12" s="9" t="inlineStr">
-        <is>
-          <t>注）介護報酬の改定は3年ごとに行われ、介護保険事業計画の期間と同期しています。令和9年度は第10期の初年度であり、改定の年に当たります。
-「構成町の意見への回答と工程の前倒し案」の「第10期は令和9年度が改定の年に当たらない」との記述は誤りであり、本作業で修正しました。</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="3" t="inlineStr">
+    <row r="13" ht="72" customHeight="1">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>注1）介護報酬の改定は3年ごとに行われ、介護保険事業計画の期間と同期しています。令和9年度は第10期の初年度であり、改定の年に当たります。
+注2）これに加えて、令和8年度に改定が行われることが令和8年3月の全国課長会議資料に示されています（「令和9年度介護報酬改定を待たずに…令和8年度介護報酬改定を行う」）。
+注3）当方の算定は令和7年度の単価を固定しているため、令和8年度改定と令和9年度改定の2回分が織り込まれていません。改定率1％当たりの効きは1回分の値であり、2回分では倍になります。
+注4）「構成町の意見への回答と工程の前倒し案」の「第10期は令和9年度が改定の年に当たらない」との記述は誤りであり、本作業で修正しました。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>2　当区域の単価の実績（構成を固定した指数）</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="32" customHeight="1">
-      <c r="A15" s="4" t="n"/>
-      <c r="B15" s="4" t="inlineStr">
+    <row r="16" ht="32" customHeight="1">
+      <c r="A16" s="4" t="n"/>
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>年度</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>単価指数</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr">
         <is>
           <t>対前年</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="E16" s="4" t="inlineStr">
         <is>
           <t>改定の有無</t>
         </is>
       </c>
-      <c r="F15" s="4" t="n"/>
-      <c r="G15" s="4" t="inlineStr">
+      <c r="F16" s="4" t="n"/>
+      <c r="G16" s="4" t="inlineStr">
         <is>
           <t>備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="5" t="n"/>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>H30</t>
-        </is>
-      </c>
-      <c r="C16" s="11" t="n">
-        <v>100</v>
-      </c>
-      <c r="D16" s="5" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>改定（平成30年4月）</t>
-        </is>
-      </c>
-      <c r="F16" s="5" t="n"/>
-      <c r="G16" s="5" t="inlineStr">
-        <is>
-          <t>基準</t>
         </is>
       </c>
     </row>
@@ -22452,43 +22454,47 @@
       <c r="A17" s="5" t="n"/>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>R元</t>
+          <t>H30</t>
         </is>
       </c>
       <c r="C17" s="11" t="n">
-        <v>101.317</v>
-      </c>
-      <c r="D17" s="10" t="inlineStr">
-        <is>
-          <t>+1.32％</t>
+        <v>100</v>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>改定（令和元年10月・半年分）</t>
+          <t>改定（平成30年4月）</t>
         </is>
       </c>
       <c r="F17" s="5" t="n"/>
-      <c r="G17" s="5" t="n"/>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>基準</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="5" t="n"/>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R元</t>
         </is>
       </c>
       <c r="C18" s="11" t="n">
-        <v>104.12</v>
-      </c>
-      <c r="D18" s="5" t="inlineStr">
-        <is>
-          <t>+2.77％</t>
+        <v>101.317</v>
+      </c>
+      <c r="D18" s="10" t="inlineStr">
+        <is>
+          <t>+1.32％</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>改定（令和元年10月・半年分）</t>
         </is>
       </c>
       <c r="F18" s="5" t="n"/>
@@ -22498,20 +22504,20 @@
       <c r="A19" s="5" t="n"/>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>R3</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="C19" s="11" t="n">
-        <v>105.354</v>
-      </c>
-      <c r="D19" s="10" t="inlineStr">
-        <is>
-          <t>+1.18％</t>
+        <v>104.12</v>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>+2.77％</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>改定（令和3年4月）</t>
+          <t>―</t>
         </is>
       </c>
       <c r="F19" s="5" t="n"/>
@@ -22521,20 +22527,20 @@
       <c r="A20" s="5" t="n"/>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>R4</t>
+          <t>R3</t>
         </is>
       </c>
       <c r="C20" s="11" t="n">
-        <v>106.558</v>
+        <v>105.354</v>
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>+1.14％</t>
+          <t>+1.18％</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>加算（令和4年10月・半年分）</t>
+          <t>改定（令和3年4月）</t>
         </is>
       </c>
       <c r="F20" s="5" t="n"/>
@@ -22544,20 +22550,20 @@
       <c r="A21" s="5" t="n"/>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>R5</t>
+          <t>R4</t>
         </is>
       </c>
       <c r="C21" s="11" t="n">
-        <v>107.705</v>
-      </c>
-      <c r="D21" s="5" t="inlineStr">
-        <is>
-          <t>+1.08％</t>
+        <v>106.558</v>
+      </c>
+      <c r="D21" s="10" t="inlineStr">
+        <is>
+          <t>+1.14％</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>加算（令和4年10月・半年分）</t>
         </is>
       </c>
       <c r="F21" s="5" t="n"/>
@@ -22567,20 +22573,20 @@
       <c r="A22" s="5" t="n"/>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>R6</t>
+          <t>R5</t>
         </is>
       </c>
       <c r="C22" s="11" t="n">
-        <v>109.893</v>
-      </c>
-      <c r="D22" s="10" t="inlineStr">
-        <is>
-          <t>+2.03％</t>
+        <v>107.705</v>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>+1.08％</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>改定（令和6年4月）</t>
+          <t>―</t>
         </is>
       </c>
       <c r="F22" s="5" t="n"/>
@@ -22590,54 +22596,77 @@
       <c r="A23" s="5" t="n"/>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>R7</t>
+          <t>R6</t>
         </is>
       </c>
       <c r="C23" s="11" t="n">
-        <v>112.929</v>
-      </c>
-      <c r="D23" s="5" t="inlineStr">
-        <is>
-          <t>+2.76％</t>
+        <v>109.893</v>
+      </c>
+      <c r="D23" s="10" t="inlineStr">
+        <is>
+          <t>+2.03％</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>改定（令和6年4月）</t>
         </is>
       </c>
       <c r="F23" s="5" t="n"/>
       <c r="G23" s="5" t="n"/>
     </row>
-    <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="19" t="n"/>
-      <c r="B24" s="19" t="inlineStr">
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="5" t="n"/>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>R7</t>
+        </is>
+      </c>
+      <c r="C24" s="11" t="n">
+        <v>112.929</v>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>+2.76％</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="n"/>
+      <c r="G24" s="5" t="n"/>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="19" t="n"/>
+      <c r="B25" s="19" t="inlineStr">
         <is>
           <t>7年計</t>
         </is>
       </c>
-      <c r="C24" s="20" t="n">
+      <c r="C25" s="20" t="n">
         <v>112.929</v>
       </c>
-      <c r="D24" s="19" t="inlineStr">
+      <c r="D25" s="19" t="inlineStr">
         <is>
           <t>+12.93％</t>
         </is>
       </c>
-      <c r="E24" s="19" t="inlineStr">
+      <c r="E25" s="19" t="inlineStr">
         <is>
           <t>年率+1.75％</t>
         </is>
       </c>
-      <c r="F24" s="19" t="n"/>
-      <c r="G24" s="19" t="inlineStr">
+      <c r="F25" s="19" t="n"/>
+      <c r="G25" s="19" t="inlineStr">
         <is>
           <t>中央値+1.32％</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="62" customHeight="1">
-      <c r="A25" s="9" t="inlineStr">
+    <row r="26" ht="62" customHeight="1">
+      <c r="A26" s="9" t="inlineStr">
         <is>
           <t>注1）単価指数は、前年の利用者構成で固定した連鎖ラスパイレス指数です。　　指数＝Σ(前年の利用者数×当年の1人あたり給付費)÷Σ(前年の利用者数×前年の1人あたり給付費)
 注2）構成を固定しないと、単価の低い在宅サービスの比重が上がることにより総額の単価が下がり、改定の効果が見えなくなります。
@@ -22645,77 +22674,52 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="3" t="inlineStr">
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="3" t="inlineStr">
         <is>
           <t>3　単価の伸びの内訳</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="32" customHeight="1">
-      <c r="A28" s="4" t="inlineStr">
+    <row r="29" ht="32" customHeight="1">
+      <c r="A29" s="4" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B28" s="4" t="inlineStr">
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>年率</t>
         </is>
       </c>
-      <c r="C28" s="4" t="inlineStr">
+      <c r="C29" s="4" t="inlineStr">
         <is>
           <t>測り方</t>
         </is>
       </c>
-      <c r="D28" s="4" t="n"/>
-      <c r="E28" s="4" t="n"/>
-      <c r="F28" s="4" t="n"/>
-      <c r="G28" s="4" t="inlineStr">
+      <c r="D29" s="4" t="n"/>
+      <c r="E29" s="4" t="n"/>
+      <c r="F29" s="4" t="n"/>
+      <c r="G29" s="4" t="inlineStr">
         <is>
           <t>内容</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="26" customHeight="1">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>単価（1人あたり給付費）</t>
-        </is>
-      </c>
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>+1.75％</t>
-        </is>
-      </c>
-      <c r="C29" s="5" t="inlineStr">
-        <is>
-          <t>構成を固定した連鎖ラスパイレス指数</t>
-        </is>
-      </c>
-      <c r="D29" s="5" t="n"/>
-      <c r="E29" s="5" t="n"/>
-      <c r="F29" s="5" t="n"/>
-      <c r="G29" s="5" t="inlineStr">
-        <is>
-          <t>報酬改定・加算の算定・要介護度の重度化・利用量の合計</t>
         </is>
       </c>
     </row>
     <row r="30" ht="26" customHeight="1">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>1人1月あたり利用日数・回数</t>
+          <t>単価（1人あたり給付費）</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>+0.25％</t>
+          <t>+1.75％</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>総括表詳細（３）の14系列の中央値（平成30年度→令和7年度）</t>
+          <t>構成を固定した連鎖ラスパイレス指数</t>
         </is>
       </c>
       <c r="D30" s="5" t="n"/>
@@ -22723,24 +22727,24 @@
       <c r="F30" s="5" t="n"/>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>利用量による分</t>
+          <t>報酬改定・加算の算定・要介護度の重度化・利用量の合計</t>
         </is>
       </c>
     </row>
     <row r="31" ht="26" customHeight="1">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>差（利用量以外の分）</t>
+          <t>1人1月あたり利用日数・回数</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>+1.51％</t>
+          <t>+0.25％</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>上の2つの差</t>
+          <t>総括表詳細（３）の14系列の中央値（平成30年度→令和7年度）</t>
         </is>
       </c>
       <c r="D31" s="5" t="n"/>
@@ -22748,298 +22752,300 @@
       <c r="F31" s="5" t="n"/>
       <c r="G31" s="5" t="inlineStr">
         <is>
+          <t>利用量による分</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="26" customHeight="1">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>差（利用量以外の分）</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>+1.51％</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>上の2つの差</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="n"/>
+      <c r="E32" s="5" t="n"/>
+      <c r="F32" s="5" t="n"/>
+      <c r="G32" s="5" t="inlineStr">
+        <is>
           <t>報酬改定・加算の算定・要介護度の重度化による分</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="48" customHeight="1">
-      <c r="A32" s="9" t="inlineStr">
+    <row r="33" ht="48" customHeight="1">
+      <c r="A33" s="9" t="inlineStr">
         <is>
           <t>注）単価の伸び（年率+1.75％）のうち、利用量による分は+0.25％にとどまります。残り+1.51％は報酬改定・加算の算定・要介護度の重度化によるものです。改定の有無で単価の伸びに差が見られないことと合わせると、改定率を外から与えなくても、単価の実績の趨勢を置くことで実質的に改定を織り込めることになります。</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="20" customHeight="1">
-      <c r="A34" s="3" t="inlineStr">
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="3" t="inlineStr">
         <is>
           <t>4　単価の置き方と月額</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="32" customHeight="1">
-      <c r="A35" s="4" t="n"/>
-      <c r="B35" s="4" t="inlineStr">
+    <row r="36" ht="32" customHeight="1">
+      <c r="A36" s="4" t="n"/>
+      <c r="B36" s="4" t="inlineStr">
         <is>
           <t>置き方</t>
         </is>
       </c>
-      <c r="C35" s="4" t="inlineStr">
+      <c r="C36" s="4" t="inlineStr">
         <is>
           <t>令和9年度</t>
         </is>
       </c>
-      <c r="D35" s="4" t="inlineStr">
+      <c r="D36" s="4" t="inlineStr">
         <is>
           <t>令和11年度</t>
         </is>
       </c>
-      <c r="E35" s="4" t="inlineStr">
+      <c r="E36" s="4" t="inlineStr">
         <is>
           <t>給付費（3か年）</t>
         </is>
       </c>
-      <c r="F35" s="4" t="inlineStr">
+      <c r="F36" s="4" t="inlineStr">
         <is>
           <t>月額</t>
         </is>
       </c>
-      <c r="G35" s="4" t="inlineStr">
+      <c r="G36" s="4" t="inlineStr">
         <is>
           <t>差</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="24" customHeight="1">
-      <c r="A36" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t>① 令和7年度で固定（採用パターンP3）</t>
-        </is>
-      </c>
-      <c r="C36" s="5" t="inlineStr">
-        <is>
-          <t>+0.0％</t>
-        </is>
-      </c>
-      <c r="D36" s="5" t="inlineStr">
-        <is>
-          <t>+0.0％</t>
-        </is>
-      </c>
-      <c r="E36" s="11" t="n">
-        <v>9020.200000000001</v>
-      </c>
-      <c r="F36" s="6" t="inlineStr">
-        <is>
-          <t>6428円</t>
-        </is>
-      </c>
-      <c r="G36" s="5" t="inlineStr">
-        <is>
-          <t>+0円</t>
         </is>
       </c>
     </row>
     <row r="37" ht="24" customHeight="1">
       <c r="A37" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>② 実績の趨勢 年率+1.75％（平均）</t>
+          <t>① 令和7年度で固定（採用パターンP3）</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>+3.5％</t>
+          <t>+0.0％</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>+7.2％</t>
+          <t>+0.0％</t>
         </is>
       </c>
       <c r="E37" s="11" t="n">
-        <v>9505.5</v>
-      </c>
-      <c r="F37" s="5" t="inlineStr">
-        <is>
-          <t>6755円</t>
+        <v>9020.200000000001</v>
+      </c>
+      <c r="F37" s="6" t="inlineStr">
+        <is>
+          <t>6428円</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>+327円</t>
+          <t>+0円</t>
         </is>
       </c>
     </row>
     <row r="38" ht="24" customHeight="1">
       <c r="A38" s="11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>③ 実績の趨勢 年率+1.32％（中央値）</t>
+          <t>② 実績の趨勢 年率+1.75％（平均）</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>+2.7％</t>
+          <t>+3.5％</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>+5.4％</t>
+          <t>+7.2％</t>
         </is>
       </c>
       <c r="E38" s="11" t="n">
-        <v>9382.700000000001</v>
+        <v>9505.5</v>
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>6672円</t>
+          <t>6755円</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>+244円</t>
+          <t>+327円</t>
         </is>
       </c>
     </row>
     <row r="39" ht="24" customHeight="1">
       <c r="A39" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>④ 年率＋1.0％</t>
+          <t>③ 実績の趨勢 年率+1.32％（中央値）</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>+2.0％</t>
+          <t>+2.7％</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>+4.1％</t>
+          <t>+5.4％</t>
         </is>
       </c>
       <c r="E39" s="11" t="n">
-        <v>9294.5</v>
+        <v>9382.700000000001</v>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>6613円</t>
+          <t>6672円</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>+185円</t>
+          <t>+244円</t>
         </is>
       </c>
     </row>
     <row r="40" ht="24" customHeight="1">
       <c r="A40" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>④ 年率＋1.0％</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>+2.0％</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>+4.1％</t>
+        </is>
+      </c>
+      <c r="E40" s="11" t="n">
+        <v>9294.5</v>
+      </c>
+      <c r="F40" s="5" t="inlineStr">
+        <is>
+          <t>6613円</t>
+        </is>
+      </c>
+      <c r="G40" s="5" t="inlineStr">
+        <is>
+          <t>+185円</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="24" customHeight="1">
+      <c r="A41" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="B40" s="5" t="inlineStr">
+      <c r="B41" s="5" t="inlineStr">
         <is>
           <t>⑤ 年率＋2.0％</t>
         </is>
       </c>
-      <c r="C40" s="5" t="inlineStr">
+      <c r="C41" s="5" t="inlineStr">
         <is>
           <t>+4.0％</t>
         </is>
       </c>
-      <c r="D40" s="5" t="inlineStr">
+      <c r="D41" s="5" t="inlineStr">
         <is>
           <t>+8.2％</t>
         </is>
       </c>
-      <c r="E40" s="11" t="n">
+      <c r="E41" s="11" t="n">
         <v>9574.9</v>
       </c>
-      <c r="F40" s="5" t="inlineStr">
+      <c r="F41" s="5" t="inlineStr">
         <is>
           <t>6802円</t>
         </is>
       </c>
-      <c r="G40" s="5" t="inlineStr">
+      <c r="G41" s="5" t="inlineStr">
         <is>
           <t>+374円</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="20" customHeight="1">
-      <c r="A42" s="3" t="inlineStr">
+    <row r="43" ht="20" customHeight="1">
+      <c r="A43" s="3" t="inlineStr">
         <is>
           <t>5　改定率のみを別に置く場合</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="32" customHeight="1">
-      <c r="A43" s="4" t="inlineStr">
+    <row r="44" ht="32" customHeight="1">
+      <c r="A44" s="4" t="inlineStr">
         <is>
           <t>改定率</t>
         </is>
       </c>
-      <c r="B43" s="4" t="inlineStr">
+      <c r="B44" s="4" t="inlineStr">
         <is>
           <t>給付費（3か年）</t>
         </is>
       </c>
-      <c r="C43" s="4" t="inlineStr">
+      <c r="C44" s="4" t="inlineStr">
         <is>
           <t>月額</t>
         </is>
       </c>
-      <c r="D43" s="4" t="inlineStr">
+      <c r="D44" s="4" t="inlineStr">
         <is>
           <t>差</t>
         </is>
       </c>
-      <c r="E43" s="4" t="n"/>
-      <c r="F43" s="4" t="n"/>
-      <c r="G43" s="4" t="inlineStr">
+      <c r="E44" s="4" t="n"/>
+      <c r="F44" s="4" t="n"/>
+      <c r="G44" s="4" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-    </row>
-    <row r="44" ht="20" customHeight="1">
-      <c r="A44" s="5" t="inlineStr">
-        <is>
-          <t>-0.50％</t>
-        </is>
-      </c>
-      <c r="B44" s="11" t="n">
-        <v>8975.1</v>
-      </c>
-      <c r="C44" s="5" t="inlineStr">
-        <is>
-          <t>6398円</t>
-        </is>
-      </c>
-      <c r="D44" s="5" t="inlineStr">
-        <is>
-          <t>-30円</t>
-        </is>
-      </c>
-      <c r="E44" s="5" t="n"/>
-      <c r="F44" s="5" t="n"/>
-      <c r="G44" s="5" t="n"/>
     </row>
     <row r="45" ht="20" customHeight="1">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>+0.00％</t>
+          <t>-0.50％</t>
         </is>
       </c>
       <c r="B45" s="11" t="n">
-        <v>9020.200000000001</v>
+        <v>8975.1</v>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>6428円</t>
+          <t>6398円</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>+0円</t>
+          <t>-30円</t>
         </is>
       </c>
       <c r="E45" s="5" t="n"/>
@@ -23049,20 +23055,20 @@
     <row r="46" ht="20" customHeight="1">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>+0.50％</t>
+          <t>+0.00％</t>
         </is>
       </c>
       <c r="B46" s="11" t="n">
-        <v>9065.299999999999</v>
+        <v>9020.200000000001</v>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>6459円</t>
+          <t>6428円</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>+30円</t>
+          <t>+0円</t>
         </is>
       </c>
       <c r="E46" s="5" t="n"/>
@@ -23072,78 +23078,101 @@
     <row r="47" ht="20" customHeight="1">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>+1.00％</t>
+          <t>+0.50％</t>
         </is>
       </c>
       <c r="B47" s="11" t="n">
-        <v>9110.4</v>
+        <v>9065.299999999999</v>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>6489円</t>
+          <t>6459円</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>+61円</t>
+          <t>+30円</t>
         </is>
       </c>
       <c r="E47" s="5" t="n"/>
       <c r="F47" s="5" t="n"/>
-      <c r="G47" s="5" t="inlineStr">
-        <is>
-          <t>改定率1％あたり月額+61円</t>
-        </is>
-      </c>
+      <c r="G47" s="5" t="n"/>
     </row>
     <row r="48" ht="20" customHeight="1">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>+1.50％</t>
+          <t>+1.00％</t>
         </is>
       </c>
       <c r="B48" s="11" t="n">
-        <v>9155.5</v>
+        <v>9110.4</v>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>6519円</t>
+          <t>6489円</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>+91円</t>
+          <t>+61円</t>
         </is>
       </c>
       <c r="E48" s="5" t="n"/>
       <c r="F48" s="5" t="n"/>
-      <c r="G48" s="5" t="n"/>
+      <c r="G48" s="5" t="inlineStr">
+        <is>
+          <t>改定率1％あたり月額+61円</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="20" customHeight="1">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>+2.00％</t>
+          <t>+1.50％</t>
         </is>
       </c>
       <c r="B49" s="11" t="n">
-        <v>9200.6</v>
+        <v>9155.5</v>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>6550円</t>
+          <t>6519円</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>+121円</t>
+          <t>+91円</t>
         </is>
       </c>
       <c r="E49" s="5" t="n"/>
       <c r="F49" s="5" t="n"/>
       <c r="G49" s="5" t="n"/>
     </row>
-    <row r="50" ht="58" customHeight="1">
-      <c r="A50" s="9" t="inlineStr">
+    <row r="50" ht="20" customHeight="1">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>+2.00％</t>
+        </is>
+      </c>
+      <c r="B50" s="11" t="n">
+        <v>9200.6</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>6550円</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="inlineStr">
+        <is>
+          <t>+121円</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="n"/>
+      <c r="F50" s="5" t="n"/>
+      <c r="G50" s="5" t="n"/>
+    </row>
+    <row r="51" ht="58" customHeight="1">
+      <c r="A51" s="9" t="inlineStr">
         <is>
           <t>注1）改定率1％あたり月額+61円です。
 注2）単価を令和7年度で固定したまま改定率のみを乗じる方法は、実績の趨勢（年率+1.75％）を落としたままになります。改定率が告示されたら、趨勢と改定率のどちらを採るかではなく、趨勢のうち改定による分と改定以外の分をどう分けるかの問題になります。
@@ -23153,17 +23182,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A32:G32"/>
-    <mergeCell ref="A14:G14"/>
+    <mergeCell ref="A13:G13"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A27:G27"/>
-    <mergeCell ref="A34:G34"/>
-    <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A35:G35"/>
     <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A50:G50"/>
+    <mergeCell ref="A26:G26"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A25:G25"/>
-    <mergeCell ref="A42:G42"/>
+    <mergeCell ref="A15:G15"/>
+    <mergeCell ref="A43:G43"/>
+    <mergeCell ref="A33:G33"/>
+    <mergeCell ref="A51:G51"/>
+    <mergeCell ref="A28:G28"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -23849,7 +23878,7 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>令和9年度は改定の年に当たりますが改定率は未告示です。当区域の単価指数は7年で+12.93％（年率+1.75％）伸びており、改定のあった年（平均+1.42％）となかった年（平均+2.20％）で差が見られません。利用日数・回数の伸びは年率+0.25％にとどまるため、残りは報酬改定・加算の算定・要介護度の重度化によるものです。単価を固定していることは月額で+244円から+327円に当たります。</t>
+          <t>令和9年度は改定の年に当たりますが改定率は未告示です。加えて令和8年度にも改定が行われるため、令和7年度の単価を固定すると2回分の改定を落とすことになります。当区域の単価指数は7年で+12.93％（年率+1.75％）伸びており、改定のあった年（平均+1.42％）となかった年（平均+2.20％）で差が見られません。利用日数・回数の伸びは年率+0.25％にとどまるため、残りは報酬改定・加算の算定・要介護度の重度化によるものです。単価を固定していることは月額で+244円から+327円に当たります。</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">

--- a/output/第10期計画_サービス見込量算定_統合報告書.xlsx
+++ b/output/第10期計画_サービス見込量算定_統合報告書.xlsx
@@ -24883,7 +24883,7 @@
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>内部保管23件</t>
+          <t>内部保管25件</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">

--- a/output/第10期計画_サービス見込量算定_統合報告書.xlsx
+++ b/output/第10期計画_サービス見込量算定_統合報告書.xlsx
@@ -8721,7 +8721,7 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>単価は改定の有無に関係なく年率1.75％で伸びている（構成を固定した連鎖ラスパイレス指数で7年＋12.93％）。令和9年度は報酬改定の年（3年周期。平成30・令和3・令和6の次）。固定していることは月額で＋185〜＋374円に当たる</t>
+          <t>単価は改定の有無に関係なく年率1.75％で伸びている（構成を固定した連鎖ラスパイレス指数で7年＋12.93％）。令和9年度は報酬改定の年（3年周期。平成30・令和3・令和6の次）。固定していることは単価の趨勢を落としており、月額への効きは第10章及び第6章による</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -16152,7 +16152,7 @@
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>＋185〜＋374円</t>
+          <t>第10章による</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">

--- a/output/第10期計画_サービス見込量算定_統合報告書.xlsx
+++ b/output/第10期計画_サービス見込量算定_統合報告書.xlsx
@@ -25082,7 +25082,7 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>サービス見込量 第1次概算
+          <t>サービス見込量の算定
 計画素案 第6章第4節4</t>
         </is>
       </c>

--- a/output/第10期計画_サービス見込量算定_統合報告書.xlsx
+++ b/output/第10期計画_サービス見込量算定_統合報告書.xlsx
@@ -24883,7 +24883,7 @@
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>内部保管25件</t>
+          <t>内部保管26件</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
